--- a/salidas/empresas/SYK.xlsx
+++ b/salidas/empresas/SYK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>39.68034362792969</v>
+        <v>39.68035888671875</v>
       </c>
       <c r="C2" t="n">
         <v>49.90000152587891</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>36.75400924682617</v>
+        <v>36.75402069091797</v>
       </c>
       <c r="C3" t="n">
         <v>46.22000122070312</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>35.2590446472168</v>
+        <v>35.25902938842773</v>
       </c>
       <c r="C4" t="n">
         <v>44.34000015258789</v>
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>34.90916061401367</v>
+        <v>34.90917205810547</v>
       </c>
       <c r="C6" t="n">
         <v>43.90000152587891</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.48576736450195</v>
+        <v>33.48574447631836</v>
       </c>
       <c r="C7" t="n">
         <v>42.11000061035156</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>36.18942642211914</v>
+        <v>36.18943023681641</v>
       </c>
       <c r="C8" t="n">
         <v>45.5099983215332</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>38.19332504272461</v>
+        <v>38.19331741333008</v>
       </c>
       <c r="C9" t="n">
         <v>48.02999877929688</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>39.43380737304688</v>
+        <v>39.43381881713867</v>
       </c>
       <c r="C10" t="n">
         <v>49.59000015258789</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>41.58086395263672</v>
+        <v>41.58083724975586</v>
       </c>
       <c r="C11" t="n">
         <v>52.29000091552734</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>41.23892593383789</v>
+        <v>41.23892211914062</v>
       </c>
       <c r="C12" t="n">
         <v>51.86000061035156</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>43.99885177612305</v>
+        <v>43.99886322021484</v>
       </c>
       <c r="C13" t="n">
         <v>55.11000061035156</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>49.45180892944336</v>
+        <v>49.45181274414062</v>
       </c>
       <c r="C14" t="n">
         <v>61.93999862670898</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>49.51567840576172</v>
+        <v>49.51569366455078</v>
       </c>
       <c r="C15" t="n">
         <v>62.02000045776367</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>52.94871139526367</v>
+        <v>52.94872283935547</v>
       </c>
       <c r="C16" t="n">
         <v>66.31999969482422</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>51.84698486328125</v>
+        <v>51.84696960449219</v>
       </c>
       <c r="C17" t="n">
         <v>64.94000244140625</v>
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>50.36994171142578</v>
+        <v>50.36994934082031</v>
       </c>
       <c r="C19" t="n">
         <v>63.09000015258789</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>49.843017578125</v>
+        <v>49.84299850463867</v>
       </c>
       <c r="C20" t="n">
         <v>62.43000030517578</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>53.33194732666016</v>
+        <v>53.33196258544922</v>
       </c>
       <c r="C21" t="n">
         <v>66.80000305175781</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>56.68515396118164</v>
+        <v>56.68515777587891</v>
       </c>
       <c r="C23" t="n">
         <v>71</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.98652648925781</v>
+        <v>57.98649978637695</v>
       </c>
       <c r="C24" t="n">
         <v>72.62999725341797</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>59.91365814208984</v>
+        <v>59.91365051269531</v>
       </c>
       <c r="C25" t="n">
         <v>74.72000122070312</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>53.69937896728516</v>
+        <v>53.69938278198242</v>
       </c>
       <c r="C26" t="n">
         <v>66.97000122070312</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>52.20796585083008</v>
+        <v>52.20795822143555</v>
       </c>
       <c r="C27" t="n">
         <v>65.11000061035156</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>52.15984344482422</v>
+        <v>52.15983200073242</v>
       </c>
       <c r="C28" t="n">
         <v>65.05000305175781</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>51.98345184326172</v>
+        <v>51.98342895507812</v>
       </c>
       <c r="C29" t="n">
         <v>64.83000183105469</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>51.75892639160156</v>
+        <v>51.7589225769043</v>
       </c>
       <c r="C30" t="n">
         <v>64.55000305175781</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>50.41984558105469</v>
+        <v>50.41984939575195</v>
       </c>
       <c r="C31" t="n">
         <v>62.88000106811523</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>51.47025680541992</v>
+        <v>51.47025299072266</v>
       </c>
       <c r="C32" t="n">
         <v>64.19000244140625</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>53.87576675415039</v>
+        <v>53.87580108642578</v>
       </c>
       <c r="C33" t="n">
         <v>67.19000244140625</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>49.95477676391602</v>
+        <v>49.95476531982422</v>
       </c>
       <c r="C34" t="n">
         <v>62.29999923706055</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>42.86647033691406</v>
+        <v>42.86649703979492</v>
       </c>
       <c r="C35" t="n">
         <v>53.45999908447266</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>31.20770072937012</v>
+        <v>31.20770454406738</v>
       </c>
       <c r="C36" t="n">
         <v>38.91999816894531</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>32.35863876342773</v>
+        <v>32.35866165161133</v>
       </c>
       <c r="C37" t="n">
         <v>39.95000076293945</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>34.21349716186523</v>
+        <v>34.2135009765625</v>
       </c>
       <c r="C38" t="n">
         <v>42.2400016784668</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>27.27198219299316</v>
+        <v>27.27197456359863</v>
       </c>
       <c r="C39" t="n">
         <v>33.66999816894531</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>31.35427665710449</v>
+        <v>31.35426902770996</v>
       </c>
       <c r="C41" t="n">
         <v>38.70999908447266</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>31.13557434082031</v>
+        <v>31.13557815551758</v>
       </c>
       <c r="C42" t="n">
         <v>38.43999862670898</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.18855667114258</v>
+        <v>32.18854904174805</v>
       </c>
       <c r="C43" t="n">
         <v>39.7400016784668</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>31.49197578430176</v>
+        <v>31.49197769165039</v>
       </c>
       <c r="C44" t="n">
         <v>38.88000106811523</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>33.58170700073242</v>
+        <v>33.58171463012695</v>
       </c>
       <c r="C45" t="n">
         <v>41.45999908447266</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>36.79733657836914</v>
+        <v>36.79733276367188</v>
       </c>
       <c r="C46" t="n">
         <v>45.43000030517578</v>
@@ -1343,11 +1355,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>37.25901031494141</v>
+        <v>37.25902557373047</v>
       </c>
       <c r="C47" t="n">
         <v>46</v>
@@ -1368,11 +1380,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.90615081787109</v>
+        <v>40.90614318847656</v>
       </c>
       <c r="C48" t="n">
         <v>50.40000152587891</v>
@@ -1393,11 +1405,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>41.00209426879883</v>
+        <v>41.00207901000977</v>
       </c>
       <c r="C49" t="n">
         <v>50.36999893188477</v>
@@ -1418,11 +1430,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>42.26380157470703</v>
+        <v>42.26379776000977</v>
       </c>
       <c r="C50" t="n">
         <v>51.91999816894531</v>
@@ -1443,11 +1455,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>43.22434234619141</v>
+        <v>43.22434616088867</v>
       </c>
       <c r="C51" t="n">
         <v>53.09999847412109</v>
@@ -1468,11 +1480,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>46.69955825805664</v>
+        <v>46.69954681396484</v>
       </c>
       <c r="C52" t="n">
         <v>57.22000122070312</v>
@@ -1493,11 +1505,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>46.87907409667969</v>
+        <v>46.87908935546875</v>
       </c>
       <c r="C53" t="n">
         <v>57.43999862670898</v>
@@ -1518,7 +1530,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1543,11 +1555,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.97865676879883</v>
+        <v>40.97867584228516</v>
       </c>
       <c r="C55" t="n">
         <v>50.06000137329102</v>
@@ -1568,7 +1580,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1593,11 +1605,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>35.35493850708008</v>
+        <v>35.35495376586914</v>
       </c>
       <c r="C57" t="n">
         <v>43.18999862670898</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>41.09591293334961</v>
+        <v>41.09590530395508</v>
       </c>
       <c r="C58" t="n">
         <v>50.04999923706055</v>
@@ -1643,11 +1655,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>40.63608932495117</v>
+        <v>40.63609313964844</v>
       </c>
       <c r="C59" t="n">
         <v>49.4900016784668</v>
@@ -1668,11 +1680,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>41.12873840332031</v>
+        <v>41.12875366210938</v>
       </c>
       <c r="C60" t="n">
         <v>50.09000015258789</v>
@@ -1693,7 +1705,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1718,11 +1730,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>47.4202766418457</v>
+        <v>47.42026901245117</v>
       </c>
       <c r="C62" t="n">
         <v>57.56000137329102</v>
@@ -1743,11 +1755,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>52.11614608764648</v>
+        <v>52.11614227294922</v>
       </c>
       <c r="C63" t="n">
         <v>63.2599983215332</v>
@@ -1772,11 +1784,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>50.23845672607422</v>
+        <v>50.23846435546875</v>
       </c>
       <c r="C64" t="n">
         <v>60.79999923706055</v>
@@ -1801,11 +1813,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>48.75113296508789</v>
+        <v>48.75114440917969</v>
       </c>
       <c r="C65" t="n">
         <v>59</v>
@@ -1830,11 +1842,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>51.56053161621094</v>
+        <v>51.56052398681641</v>
       </c>
       <c r="C66" t="n">
         <v>62.40000152587891</v>
@@ -1859,11 +1871,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>48.64611053466797</v>
+        <v>48.6461181640625</v>
       </c>
       <c r="C67" t="n">
         <v>58.68999862670898</v>
@@ -1888,11 +1900,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>45.04055023193359</v>
+        <v>45.04054641723633</v>
       </c>
       <c r="C68" t="n">
         <v>54.34000015258789</v>
@@ -1917,11 +1929,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>40.48179244995117</v>
+        <v>40.48178863525391</v>
       </c>
       <c r="C69" t="n">
         <v>48.84000015258789</v>
@@ -1946,7 +1958,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1975,11 +1987,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>39.85688400268555</v>
+        <v>39.85686492919922</v>
       </c>
       <c r="C71" t="n">
         <v>47.90999984741211</v>
@@ -2004,7 +2016,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2033,11 +2045,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>41.53120422363281</v>
+        <v>41.53120040893555</v>
       </c>
       <c r="C73" t="n">
         <v>49.70999908447266</v>
@@ -2062,11 +2074,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>46.31009292602539</v>
+        <v>46.31009674072266</v>
       </c>
       <c r="C74" t="n">
         <v>55.43000030517578</v>
@@ -2091,7 +2103,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2120,11 +2132,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.53095626831055</v>
+        <v>46.53095245361328</v>
       </c>
       <c r="C76" t="n">
         <v>55.47999954223633</v>
@@ -2149,11 +2161,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>45.76774597167969</v>
+        <v>45.76773834228516</v>
       </c>
       <c r="C77" t="n">
         <v>54.56999969482422</v>
@@ -2178,11 +2190,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>43.1510009765625</v>
+        <v>43.15099716186523</v>
       </c>
       <c r="C78" t="n">
         <v>51.45000076293945</v>
@@ -2207,11 +2219,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>46.3958625793457</v>
+        <v>46.39587020874023</v>
       </c>
       <c r="C79" t="n">
         <v>55.09999847412109</v>
@@ -2236,11 +2248,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>43.81084442138672</v>
+        <v>43.81083679199219</v>
       </c>
       <c r="C80" t="n">
         <v>52.02999877929688</v>
@@ -2265,11 +2277,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>44.84653091430664</v>
+        <v>44.84653472900391</v>
       </c>
       <c r="C81" t="n">
         <v>53.2599983215332</v>
@@ -2294,11 +2306,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>47.04641723632812</v>
+        <v>47.04642105102539</v>
       </c>
       <c r="C82" t="n">
         <v>55.65999984741211</v>
@@ -2323,11 +2335,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>44.4599723815918</v>
+        <v>44.45997619628906</v>
       </c>
       <c r="C83" t="n">
         <v>52.59999847412109</v>
@@ -2352,11 +2364,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>45.77854537963867</v>
+        <v>45.77854919433594</v>
       </c>
       <c r="C84" t="n">
         <v>54.15999984741211</v>
@@ -2381,7 +2393,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2410,11 +2422,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>53.20909118652344</v>
+        <v>53.20908355712891</v>
       </c>
       <c r="C86" t="n">
         <v>62.65000152587891</v>
@@ -2439,11 +2451,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>54.25373458862305</v>
+        <v>54.25370788574219</v>
       </c>
       <c r="C87" t="n">
         <v>63.88000106811523</v>
@@ -2468,11 +2480,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>55.6372184753418</v>
+        <v>55.63722991943359</v>
       </c>
       <c r="C88" t="n">
         <v>65.23999786376953</v>
@@ -2497,11 +2509,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>55.92717361450195</v>
+        <v>55.92718505859375</v>
       </c>
       <c r="C89" t="n">
         <v>65.58000183105469</v>
@@ -2526,11 +2538,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>56.61795806884766</v>
+        <v>56.61796188354492</v>
       </c>
       <c r="C90" t="n">
         <v>66.38999938964844</v>
@@ -2555,11 +2567,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>55.38583755493164</v>
+        <v>55.38584518432617</v>
       </c>
       <c r="C91" t="n">
         <v>64.68000030517578</v>
@@ -2584,11 +2596,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>60.33528137207031</v>
+        <v>60.33531188964844</v>
       </c>
       <c r="C92" t="n">
         <v>70.45999908447266</v>
@@ -2613,7 +2625,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2642,11 +2654,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>58.10151672363281</v>
+        <v>58.10151290893555</v>
       </c>
       <c r="C94" t="n">
         <v>67.58999633789062</v>
@@ -2671,11 +2683,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>63.4913444519043</v>
+        <v>63.49130249023438</v>
       </c>
       <c r="C95" t="n">
         <v>73.86000061035156</v>
@@ -2700,11 +2712,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>63.97268676757812</v>
+        <v>63.97271728515625</v>
       </c>
       <c r="C96" t="n">
         <v>74.41999816894531</v>
@@ -2729,11 +2741,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>64.85398864746094</v>
+        <v>64.85400390625</v>
       </c>
       <c r="C97" t="n">
         <v>75.13999938964844</v>
@@ -2758,11 +2770,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>66.97723388671875</v>
+        <v>66.97726440429688</v>
       </c>
       <c r="C98" t="n">
         <v>77.59999847412109</v>
@@ -2787,11 +2799,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>69.25585174560547</v>
+        <v>69.25586700439453</v>
       </c>
       <c r="C99" t="n">
         <v>80.23999786376953</v>
@@ -2816,11 +2828,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>70.58798980712891</v>
+        <v>70.58798217773438</v>
       </c>
       <c r="C100" t="n">
         <v>81.47000122070312</v>
@@ -2845,11 +2857,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>67.36483001708984</v>
+        <v>67.36484527587891</v>
       </c>
       <c r="C101" t="n">
         <v>77.75</v>
@@ -2874,11 +2886,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>73.20458221435547</v>
+        <v>73.20461273193359</v>
       </c>
       <c r="C102" t="n">
         <v>84.48999786376953</v>
@@ -2903,11 +2915,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>73.31884765625</v>
+        <v>73.31885528564453</v>
       </c>
       <c r="C103" t="n">
         <v>84.31999969482422</v>
@@ -2932,11 +2944,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>69.36248016357422</v>
+        <v>69.36248779296875</v>
       </c>
       <c r="C104" t="n">
         <v>79.76999664306641</v>
@@ -2961,11 +2973,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>72.44062042236328</v>
+        <v>72.44064331054688</v>
       </c>
       <c r="C105" t="n">
         <v>83.30999755859375</v>
@@ -2990,11 +3002,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.47927093505859</v>
+        <v>70.47928619384766</v>
       </c>
       <c r="C106" t="n">
         <v>80.75</v>
@@ -3019,11 +3031,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>76.39692687988281</v>
+        <v>76.39690399169922</v>
       </c>
       <c r="C107" t="n">
         <v>87.52999877929688</v>
@@ -3048,11 +3060,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>81.09262084960938</v>
+        <v>81.09259796142578</v>
       </c>
       <c r="C108" t="n">
         <v>92.91000366210938</v>
@@ -3077,7 +3089,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3106,11 +3118,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>79.75691223144531</v>
+        <v>79.75688934326172</v>
       </c>
       <c r="C110" t="n">
         <v>91.05000305175781</v>
@@ -3135,11 +3147,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>82.99797058105469</v>
+        <v>82.99797821044922</v>
       </c>
       <c r="C111" t="n">
         <v>94.75</v>
@@ -3164,11 +3176,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>81.11380004882812</v>
+        <v>81.11381530761719</v>
       </c>
       <c r="C112" t="n">
         <v>92.25</v>
@@ -3193,11 +3205,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>81.10497283935547</v>
+        <v>81.10501098632812</v>
       </c>
       <c r="C113" t="n">
         <v>92.23999786376953</v>
@@ -3222,11 +3234,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>84.52541351318359</v>
+        <v>84.52542114257812</v>
       </c>
       <c r="C114" t="n">
         <v>96.12999725341797</v>
@@ -3251,11 +3263,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>84.33470153808594</v>
+        <v>84.33467102050781</v>
       </c>
       <c r="C115" t="n">
         <v>95.56999969482422</v>
@@ -3280,11 +3292,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>90.24703979492188</v>
+        <v>90.24700927734375</v>
       </c>
       <c r="C116" t="n">
         <v>102.2699966430664</v>
@@ -3309,11 +3321,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>87.05258178710938</v>
+        <v>87.05260467529297</v>
       </c>
       <c r="C117" t="n">
         <v>98.65000152587891</v>
@@ -3338,11 +3350,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>83.33416748046875</v>
+        <v>83.33420562744141</v>
       </c>
       <c r="C118" t="n">
         <v>94.09999847412109</v>
@@ -3367,11 +3379,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>84.68028259277344</v>
+        <v>84.6802978515625</v>
       </c>
       <c r="C119" t="n">
         <v>95.62000274658203</v>
@@ -3396,11 +3408,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>85.4241943359375</v>
+        <v>85.42418670654297</v>
       </c>
       <c r="C120" t="n">
         <v>96.45999908447266</v>
@@ -3425,11 +3437,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>82.64118194580078</v>
+        <v>82.64116668701172</v>
       </c>
       <c r="C121" t="n">
         <v>92.94000244140625</v>
@@ -3454,11 +3466,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>88.16304016113281</v>
+        <v>88.16302490234375</v>
       </c>
       <c r="C122" t="n">
         <v>99.15000152587891</v>
@@ -3483,11 +3495,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>88.81211090087891</v>
+        <v>88.81211853027344</v>
       </c>
       <c r="C123" t="n">
         <v>99.87999725341797</v>
@@ -3512,7 +3524,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3541,11 +3553,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>97.28227996826172</v>
+        <v>97.28227233886719</v>
       </c>
       <c r="C125" t="n">
         <v>109.0100021362305</v>
@@ -3570,11 +3582,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>99.20097351074219</v>
+        <v>99.20100402832031</v>
       </c>
       <c r="C126" t="n">
         <v>111.1600036621094</v>
@@ -3599,11 +3611,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>107.29345703125</v>
+        <v>107.2934417724609</v>
       </c>
       <c r="C127" t="n">
         <v>119.8300018310547</v>
@@ -3628,11 +3640,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>104.114860534668</v>
+        <v>104.1148529052734</v>
       </c>
       <c r="C128" t="n">
         <v>116.2799987792969</v>
@@ -3657,11 +3669,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>103.559700012207</v>
+        <v>103.5597076416016</v>
       </c>
       <c r="C129" t="n">
         <v>115.6600036621094</v>
@@ -3686,11 +3698,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>104.5685501098633</v>
+        <v>104.5685653686523</v>
       </c>
       <c r="C130" t="n">
         <v>116.4100036621094</v>
@@ -3715,11 +3727,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>103.6163864135742</v>
+        <v>103.6164169311523</v>
       </c>
       <c r="C131" t="n">
         <v>115.3499984741211</v>
@@ -3744,11 +3756,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>102.0982971191406</v>
+        <v>102.0983123779297</v>
       </c>
       <c r="C132" t="n">
         <v>113.6600036621094</v>
@@ -3773,11 +3785,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>108.0024948120117</v>
+        <v>108.0025253295898</v>
       </c>
       <c r="C133" t="n">
         <v>119.8099975585938</v>
@@ -3802,7 +3814,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3831,11 +3843,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>115.8901977539062</v>
+        <v>115.8901901245117</v>
       </c>
       <c r="C135" t="n">
         <v>128.5599975585938</v>
@@ -3860,7 +3872,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3889,7 +3901,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3918,11 +3930,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>129.2851104736328</v>
+        <v>129.2851257324219</v>
       </c>
       <c r="C138" t="n">
         <v>142.9600067138672</v>
@@ -3947,11 +3959,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>125.8882522583008</v>
+        <v>125.8882446289062</v>
       </c>
       <c r="C139" t="n">
         <v>138.7799987792969</v>
@@ -3976,11 +3988,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>133.4353637695312</v>
+        <v>133.4353790283203</v>
       </c>
       <c r="C140" t="n">
         <v>147.1000061035156</v>
@@ -4005,11 +4017,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>128.2376556396484</v>
+        <v>128.2376708984375</v>
       </c>
       <c r="C141" t="n">
         <v>141.3699951171875</v>
@@ -4034,7 +4046,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4063,11 +4075,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>140.9083862304688</v>
+        <v>140.9084014892578</v>
       </c>
       <c r="C143" t="n">
         <v>154.8699951171875</v>
@@ -4092,11 +4104,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>141.9365386962891</v>
+        <v>141.9365692138672</v>
       </c>
       <c r="C144" t="n">
         <v>156</v>
@@ -4121,11 +4133,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>141.307861328125</v>
+        <v>141.3078460693359</v>
       </c>
       <c r="C145" t="n">
         <v>154.8399963378906</v>
@@ -4150,7 +4162,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4179,11 +4191,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>147.9881439208984</v>
+        <v>147.9881134033203</v>
       </c>
       <c r="C147" t="n">
         <v>162.1600036621094</v>
@@ -4208,7 +4220,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4237,7 +4249,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4266,11 +4278,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>159.2838439941406</v>
+        <v>159.2838134765625</v>
       </c>
       <c r="C150" t="n">
         <v>174.0200042724609</v>
@@ -4295,11 +4307,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>154.9914703369141</v>
+        <v>154.9914093017578</v>
       </c>
       <c r="C151" t="n">
         <v>168.8600006103516</v>
@@ -4324,11 +4336,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>149.8421936035156</v>
+        <v>149.8421783447266</v>
       </c>
       <c r="C152" t="n">
         <v>163.25</v>
@@ -4353,7 +4365,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4382,11 +4394,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>163.5242767333984</v>
+        <v>163.5242462158203</v>
       </c>
       <c r="C154" t="n">
         <v>177.6799926757812</v>
@@ -4411,7 +4423,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4440,11 +4452,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>161.4811859130859</v>
+        <v>161.4811401367188</v>
       </c>
       <c r="C156" t="n">
         <v>175.4600067138672</v>
@@ -4469,11 +4481,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>144.7486267089844</v>
+        <v>144.7486114501953</v>
       </c>
       <c r="C157" t="n">
         <v>156.75</v>
@@ -4498,11 +4510,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>163.9745330810547</v>
+        <v>163.9745483398438</v>
       </c>
       <c r="C158" t="n">
         <v>177.5700073242188</v>
@@ -4527,11 +4539,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>174.0770111083984</v>
+        <v>174.0769653320312</v>
       </c>
       <c r="C159" t="n">
         <v>188.5099945068359</v>
@@ -4556,11 +4568,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>182.8818054199219</v>
+        <v>182.8818664550781</v>
       </c>
       <c r="C160" t="n">
         <v>197.5200042724609</v>
@@ -4585,11 +4597,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>174.9099273681641</v>
+        <v>174.909912109375</v>
       </c>
       <c r="C161" t="n">
         <v>188.9100036621094</v>
@@ -4614,11 +4626,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>169.6600646972656</v>
+        <v>169.6601257324219</v>
       </c>
       <c r="C162" t="n">
         <v>183.2400054931641</v>
@@ -4643,11 +4655,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>190.8348693847656</v>
+        <v>190.8348541259766</v>
       </c>
       <c r="C163" t="n">
         <v>205.5800018310547</v>
@@ -4672,11 +4684,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>194.7336730957031</v>
+        <v>194.7336273193359</v>
       </c>
       <c r="C164" t="n">
         <v>209.7799987792969</v>
@@ -4701,7 +4713,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4730,11 +4742,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>201.2695922851562</v>
+        <v>201.2696228027344</v>
       </c>
       <c r="C166" t="n">
         <v>216.3000030517578</v>
@@ -4759,7 +4771,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4788,7 +4800,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4817,11 +4829,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>195.8865509033203</v>
+        <v>195.8865203857422</v>
       </c>
       <c r="C169" t="n">
         <v>209.9400024414062</v>
@@ -4846,7 +4858,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4875,11 +4887,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>177.8318176269531</v>
+        <v>177.8318328857422</v>
       </c>
       <c r="C171" t="n">
         <v>190.5899963378906</v>
@@ -4904,11 +4916,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>155.9081726074219</v>
+        <v>155.9081573486328</v>
       </c>
       <c r="C172" t="n">
         <v>166.4900054931641</v>
@@ -4933,7 +4945,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4962,11 +4974,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>183.2896881103516</v>
+        <v>183.2897033691406</v>
       </c>
       <c r="C174" t="n">
         <v>195.7299957275391</v>
@@ -4991,11 +5003,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>169.2976531982422</v>
+        <v>169.2976226806641</v>
       </c>
       <c r="C175" t="n">
         <v>180.1900024414062</v>
@@ -5020,11 +5032,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>181.6151733398438</v>
+        <v>181.6151580810547</v>
       </c>
       <c r="C176" t="n">
         <v>193.3000030517578</v>
@@ -5049,11 +5061,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>186.1813049316406</v>
+        <v>186.1813507080078</v>
       </c>
       <c r="C177" t="n">
         <v>198.1600036621094</v>
@@ -5078,11 +5090,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>196.3188171386719</v>
+        <v>196.3188323974609</v>
       </c>
       <c r="C178" t="n">
         <v>208.3699951171875</v>
@@ -5107,7 +5119,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5136,11 +5148,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>219.9011993408203</v>
+        <v>219.9012145996094</v>
       </c>
       <c r="C180" t="n">
         <v>233.3999938964844</v>
@@ -5165,11 +5177,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>231.4734802246094</v>
+        <v>231.4735107421875</v>
       </c>
       <c r="C181" t="n">
         <v>245.0399932861328</v>
@@ -5194,11 +5206,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>208.7738952636719</v>
+        <v>208.7738800048828</v>
       </c>
       <c r="C182" t="n">
         <v>221.0099945068359</v>
@@ -5223,11 +5235,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>229.2536010742188</v>
+        <v>229.2536163330078</v>
       </c>
       <c r="C183" t="n">
         <v>242.6900024414062</v>
@@ -5252,7 +5264,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5281,11 +5293,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>248.7371063232422</v>
+        <v>248.7370910644531</v>
       </c>
       <c r="C185" t="n">
         <v>262.6300048828125</v>
@@ -5310,7 +5322,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5339,11 +5351,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>246.5871276855469</v>
+        <v>246.5871887207031</v>
       </c>
       <c r="C187" t="n">
         <v>259.7300109863281</v>
@@ -5368,11 +5380,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>257.2299499511719</v>
+        <v>257.2298889160156</v>
       </c>
       <c r="C188" t="n">
         <v>270.9400024414062</v>
@@ -5397,7 +5409,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5426,11 +5438,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>250.965576171875</v>
+        <v>250.9656066894531</v>
       </c>
       <c r="C190" t="n">
         <v>263.7200012207031</v>
@@ -5455,11 +5467,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>253.2019348144531</v>
+        <v>253.2019653320312</v>
       </c>
       <c r="C191" t="n">
         <v>266.0700073242188</v>
@@ -5484,7 +5496,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5513,11 +5525,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>255.1407165527344</v>
+        <v>255.1406402587891</v>
       </c>
       <c r="C193" t="n">
         <v>267.4200134277344</v>
@@ -5542,11 +5554,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>236.66015625</v>
+        <v>236.6601409912109</v>
       </c>
       <c r="C194" t="n">
         <v>248.0500030517578</v>
@@ -5571,11 +5583,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>251.2576141357422</v>
+        <v>251.2575988769531</v>
       </c>
       <c r="C195" t="n">
         <v>263.3500061035156</v>
@@ -5600,11 +5612,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>255.7249908447266</v>
+        <v>255.7249450683594</v>
       </c>
       <c r="C196" t="n">
         <v>267.3500061035156</v>
@@ -5629,7 +5641,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5658,11 +5670,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>224.3034210205078</v>
+        <v>224.3033905029297</v>
       </c>
       <c r="C198" t="n">
         <v>234.5</v>
@@ -5687,7 +5699,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5716,11 +5728,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>206.136474609375</v>
+        <v>206.1364593505859</v>
       </c>
       <c r="C200" t="n">
         <v>214.75</v>
@@ -5745,11 +5757,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>196.9695281982422</v>
+        <v>196.9694671630859</v>
       </c>
       <c r="C201" t="n">
         <v>205.1999969482422</v>
@@ -5774,11 +5786,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>195.0748901367188</v>
+        <v>195.0749206542969</v>
       </c>
       <c r="C202" t="n">
         <v>202.5399932861328</v>
@@ -5803,11 +5815,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>220.7908630371094</v>
+        <v>220.7908325195312</v>
       </c>
       <c r="C203" t="n">
         <v>229.2400054931641</v>
@@ -5832,7 +5844,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5861,11 +5873,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>236.2118988037109</v>
+        <v>236.2118530273438</v>
       </c>
       <c r="C205" t="n">
         <v>244.4900054931641</v>
@@ -5890,11 +5902,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>245.2162933349609</v>
+        <v>245.2162475585938</v>
       </c>
       <c r="C206" t="n">
         <v>253.8099975585938</v>
@@ -5919,11 +5931,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>253.9792022705078</v>
+        <v>253.9791870117188</v>
       </c>
       <c r="C207" t="n">
         <v>262.8800048828125</v>
@@ -5948,7 +5960,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5977,11 +5989,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>290.2844543457031</v>
+        <v>290.284423828125</v>
       </c>
       <c r="C209" t="n">
         <v>299.6499938964844</v>
@@ -6006,7 +6018,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6035,7 +6047,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6064,11 +6076,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>275.2394409179688</v>
+        <v>275.2394714355469</v>
       </c>
       <c r="C212" t="n">
         <v>283.4100036621094</v>
@@ -6093,7 +6105,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6122,11 +6134,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>266.1407165527344</v>
+        <v>266.1406555175781</v>
       </c>
       <c r="C214" t="n">
         <v>273.2699890136719</v>
@@ -6151,11 +6163,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>263.1702575683594</v>
+        <v>263.1702270507812</v>
       </c>
       <c r="C215" t="n">
         <v>270.2200012207031</v>
@@ -6180,11 +6192,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>288.5990295410156</v>
+        <v>288.5990905761719</v>
       </c>
       <c r="C216" t="n">
         <v>296.3299865722656</v>
@@ -6209,11 +6221,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>292.4297790527344</v>
+        <v>292.4298400878906</v>
       </c>
       <c r="C217" t="n">
         <v>299.4599914550781</v>
@@ -6238,11 +6250,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>327.6042175292969</v>
+        <v>327.604248046875</v>
       </c>
       <c r="C218" t="n">
         <v>335.4800109863281</v>
@@ -6267,11 +6279,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>340.8751831054688</v>
+        <v>340.8751525878906</v>
       </c>
       <c r="C219" t="n">
         <v>349.0700073242188</v>
@@ -6296,11 +6308,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>350.2682495117188</v>
+        <v>350.268310546875</v>
       </c>
       <c r="C220" t="n">
         <v>357.8699951171875</v>
@@ -6325,7 +6337,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6354,11 +6366,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>333.8447570800781</v>
+        <v>333.8447265625</v>
       </c>
       <c r="C222" t="n">
         <v>341.0899963378906</v>
@@ -6383,7 +6395,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6412,11 +6424,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>321.2492065429688</v>
+        <v>321.2491760253906</v>
       </c>
       <c r="C224" t="n">
         <v>327.4500122070312</v>
@@ -6441,7 +6453,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6470,7 +6482,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6499,7 +6511,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6528,11 +6540,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>385.5801391601562</v>
+        <v>385.580078125</v>
       </c>
       <c r="C228" t="n">
         <v>392.1499938964844</v>
@@ -6557,11 +6569,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>354.8406982421875</v>
+        <v>354.8407287597656</v>
       </c>
       <c r="C229" t="n">
         <v>360.0499877929688</v>
@@ -6586,7 +6598,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6615,7 +6627,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6644,11 +6656,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>367.7116394042969</v>
+        <v>367.711669921875</v>
       </c>
       <c r="C232" t="n">
         <v>372.25</v>
@@ -6673,11 +6685,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>369.3612976074219</v>
+        <v>369.3612670898438</v>
       </c>
       <c r="C233" t="n">
         <v>373.9200134277344</v>
@@ -6702,11 +6714,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>377.9750061035156</v>
+        <v>377.9749755859375</v>
       </c>
       <c r="C234" t="n">
         <v>382.6400146484375</v>
@@ -6731,11 +6743,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>391.6425476074219</v>
+        <v>391.6425170898438</v>
       </c>
       <c r="C235" t="n">
         <v>395.6300048828125</v>
@@ -6760,11 +6772,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>388.7717590332031</v>
+        <v>388.7717895507812</v>
       </c>
       <c r="C236" t="n">
         <v>392.7300109863281</v>
@@ -6789,7 +6801,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6818,7 +6830,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6847,7 +6859,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6876,7 +6888,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6905,7 +6917,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6934,7 +6946,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6963,11 +6975,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>385.3855895996094</v>
+        <v>385.3856201171875</v>
       </c>
       <c r="C243" t="n">
         <v>387.4599914550781</v>
@@ -6992,7 +7004,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7021,7 +7033,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7050,7 +7062,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7079,7 +7091,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7108,7 +7120,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7137,7 +7149,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7166,32 +7178,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>273.3999938964844</v>
+        <v>269.75</v>
       </c>
       <c r="C250" t="n">
-        <v>273.3999938964844</v>
+        <v>269.75</v>
       </c>
       <c r="D250" t="n">
-        <v>53210500</v>
+        <v>55501600</v>
       </c>
       <c r="E250" t="n">
         <v>9.65</v>
       </c>
       <c r="F250" t="n">
-        <v>28.33160558512791</v>
+        <v>27.95336787564767</v>
       </c>
       <c r="G250" t="n">
         <v>383573046</v>
       </c>
       <c r="H250" t="n">
-        <v>104868868435.2559</v>
+        <v>103468829158.5</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1387232511640038</v>
+        <v>0.144696298602796</v>
       </c>
     </row>
   </sheetData>
@@ -7223,75 +7235,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7327,13 +7339,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7369,13 +7381,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7411,13 +7423,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7453,13 +7465,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7495,13 +7507,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7528,7 +7540,7 @@
       <c r="I7" t="n">
         <v>2.77</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K7" t="n">
@@ -7541,13 +7553,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7574,7 +7586,7 @@
       <c r="I8" t="n">
         <v>2.86</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K8" t="n">
@@ -7587,13 +7599,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7620,7 +7632,7 @@
       <c r="I9" t="n">
         <v>2.93</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K9" t="n">
@@ -7633,13 +7645,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7666,7 +7678,7 @@
       <c r="I10" t="n">
         <v>3.21</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K10" t="n">
@@ -7679,13 +7691,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7712,7 +7724,7 @@
       <c r="I11" t="n">
         <v>3.19</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="K11" t="n">
@@ -7725,13 +7737,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7758,7 +7770,7 @@
       <c r="I12" t="n">
         <v>3.17</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="K12" t="n">
@@ -7771,13 +7783,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7804,7 +7816,7 @@
       <c r="I13" t="n">
         <v>3.16</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="K13" t="n">
@@ -7817,13 +7829,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7850,7 +7862,7 @@
       <c r="I14" t="n">
         <v>3.15</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="K14" t="n">
@@ -7863,13 +7875,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7896,7 +7908,7 @@
       <c r="I15" t="n">
         <v>3.46</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="K15" t="n">
@@ -7909,13 +7921,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7942,7 +7954,7 @@
       <c r="I16" t="n">
         <v>3.59</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="K16" t="n">
@@ -7955,13 +7967,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7988,7 +8000,7 @@
       <c r="I17" t="n">
         <v>3.65</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="K17" t="n">
@@ -8001,13 +8013,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41204</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8034,7 +8046,7 @@
       <c r="I18" t="n">
         <v>3.73</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41204</v>
       </c>
       <c r="K18" t="n">
@@ -8047,13 +8059,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8080,7 +8092,7 @@
       <c r="I19" t="n">
         <v>3.39</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K19" t="n">
@@ -8093,13 +8105,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8126,7 +8138,7 @@
       <c r="I20" t="n">
         <v>3.27</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="K20" t="n">
@@ -8139,13 +8151,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8172,7 +8184,7 @@
       <c r="I21" t="n">
         <v>2.98</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="K21" t="n">
@@ -8185,13 +8197,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8218,7 +8230,7 @@
       <c r="I22" t="n">
         <v>2.33</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="K22" t="n">
@@ -8231,13 +8243,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8264,7 +8276,7 @@
       <c r="I23" t="n">
         <v>2.63</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="K23" t="n">
@@ -8277,13 +8289,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8310,7 +8322,7 @@
       <c r="I24" t="n">
         <v>2.02</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="K24" t="n">
@@ -8323,13 +8335,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8356,7 +8368,7 @@
       <c r="I25" t="n">
         <v>1.79</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="K25" t="n">
@@ -8369,13 +8381,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8402,7 +8414,7 @@
       <c r="I26" t="n">
         <v>1.68</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="K26" t="n">
@@ -8415,13 +8427,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8448,7 +8460,7 @@
       <c r="I27" t="n">
         <v>1.34</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="K27" t="n">
@@ -8461,13 +8473,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8494,7 +8506,7 @@
       <c r="I28" t="n">
         <v>1.74</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="K28" t="n">
@@ -8507,13 +8519,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8540,7 +8552,7 @@
       <c r="I29" t="n">
         <v>2.44</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K29" t="n">
@@ -8553,13 +8565,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8586,7 +8598,7 @@
       <c r="I30" t="n">
         <v>3.07</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="K30" t="n">
@@ -8599,13 +8611,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8632,7 +8644,7 @@
       <c r="I31" t="n">
         <v>3.78</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K31" t="n">
@@ -8645,13 +8657,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8678,7 +8690,7 @@
       <c r="I32" t="n">
         <v>4.27</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="K32" t="n">
@@ -8691,13 +8703,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8724,7 +8736,7 @@
       <c r="I33" t="n">
         <v>4.24</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="K33" t="n">
@@ -8737,13 +8749,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8770,7 +8782,7 @@
       <c r="I34" t="n">
         <v>4.39</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="K34" t="n">
@@ -8783,13 +8795,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8816,7 +8828,7 @@
       <c r="I35" t="n">
         <v>4.35</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="K35" t="n">
@@ -8829,13 +8841,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8862,7 +8874,7 @@
       <c r="I36" t="n">
         <v>4.449999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8875,13 +8887,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8908,7 +8920,7 @@
       <c r="I37" t="n">
         <v>4.48</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="K37" t="n">
@@ -8921,13 +8933,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8954,7 +8966,7 @@
       <c r="I38" t="n">
         <v>4.68</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="K38" t="n">
@@ -8967,13 +8979,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9000,7 +9012,7 @@
       <c r="I39" t="n">
         <v>2.68</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="K39" t="n">
@@ -9013,13 +9025,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9046,7 +9058,7 @@
       <c r="I40" t="n">
         <v>2.67</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="K40" t="n">
@@ -9059,13 +9071,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9092,7 +9104,7 @@
       <c r="I41" t="n">
         <v>2.83</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="K41" t="n">
@@ -9105,13 +9117,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9138,7 +9150,7 @@
       <c r="I42" t="n">
         <v>3.24</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="K42" t="n">
@@ -9151,13 +9163,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9184,7 +9196,7 @@
       <c r="I43" t="n">
         <v>9.34</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K43" t="n">
@@ -9197,13 +9209,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9230,7 +9242,7 @@
       <c r="I44" t="n">
         <v>9.270000000000001</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="K44" t="n">
@@ -9243,13 +9255,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9276,7 +9288,7 @@
       <c r="I45" t="n">
         <v>9.340000000000002</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="K45" t="n">
@@ -9289,13 +9301,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9322,7 +9334,7 @@
       <c r="I46" t="n">
         <v>9.02</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="K46" t="n">
@@ -9335,13 +9347,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9368,7 +9380,7 @@
       <c r="I47" t="n">
         <v>5.48</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="K47" t="n">
@@ -9381,13 +9393,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9414,7 +9426,7 @@
       <c r="I48" t="n">
         <v>5.69</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="K48" t="n">
@@ -9427,13 +9439,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9460,7 +9472,7 @@
       <c r="I49" t="n">
         <v>4.209999999999999</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K49" t="n">
@@ -9473,13 +9485,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9506,7 +9518,7 @@
       <c r="I50" t="n">
         <v>4.609999999999999</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="K50" t="n">
@@ -9519,13 +9531,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9552,7 +9564,7 @@
       <c r="I51" t="n">
         <v>4.2</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="K51" t="n">
@@ -9565,13 +9577,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9598,7 +9610,7 @@
       <c r="I52" t="n">
         <v>3.69</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="K52" t="n">
@@ -9611,13 +9623,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9644,7 +9656,7 @@
       <c r="I53" t="n">
         <v>5.46</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="K53" t="n">
@@ -9657,13 +9669,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9690,7 +9702,7 @@
       <c r="I54" t="n">
         <v>4.97</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K54" t="n">
@@ -9703,13 +9715,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9736,7 +9748,7 @@
       <c r="I55" t="n">
         <v>5.21</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="K55" t="n">
@@ -9749,13 +9761,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9782,7 +9794,7 @@
       <c r="I56" t="n">
         <v>5.26</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="K56" t="n">
@@ -9795,13 +9807,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9828,7 +9840,7 @@
       <c r="I57" t="n">
         <v>5.43</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K57" t="n">
@@ -9841,13 +9853,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9874,7 +9886,7 @@
       <c r="I58" t="n">
         <v>6.43</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="K58" t="n">
@@ -9887,13 +9899,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9920,7 +9932,7 @@
       <c r="I59" t="n">
         <v>6.17</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K59" t="n">
@@ -9933,13 +9945,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9966,7 +9978,7 @@
       <c r="I60" t="n">
         <v>6.87</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="K60" t="n">
@@ -9979,13 +9991,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10012,7 +10024,7 @@
       <c r="I61" t="n">
         <v>7.08</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="K61" t="n">
@@ -10025,13 +10037,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10058,7 +10070,7 @@
       <c r="I62" t="n">
         <v>6.739999999999999</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="K62" t="n">
@@ -10071,13 +10083,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10104,7 +10116,7 @@
       <c r="I63" t="n">
         <v>8.25</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="K63" t="n">
@@ -10117,13 +10129,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10150,7 +10162,7 @@
       <c r="I64" t="n">
         <v>8.76</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="K64" t="n">
@@ -10163,13 +10175,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10196,7 +10208,7 @@
       <c r="I65" t="n">
         <v>8.970000000000001</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="K65" t="n">
@@ -10209,13 +10221,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10242,7 +10254,7 @@
       <c r="I66" t="n">
         <v>9.33</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="K66" t="n">
@@ -10255,13 +10267,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10288,7 +10300,7 @@
       <c r="I67" t="n">
         <v>7.76</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="K67" t="n">
@@ -10301,13 +10313,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10334,7 +10346,7 @@
       <c r="I68" t="n">
         <v>7.4</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="K68" t="n">
@@ -10347,13 +10359,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10380,7 +10392,7 @@
       <c r="I69" t="n">
         <v>7.55</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K69" t="n">
@@ -10393,13 +10405,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10426,7 +10438,7 @@
       <c r="I70" t="n">
         <v>7.610000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K70" t="n">
@@ -10439,13 +10451,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10472,7 +10484,7 @@
       <c r="I71" t="n">
         <v>8.4</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="K71" t="n">
@@ -10485,13 +10497,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10518,7 +10530,7 @@
       <c r="I72" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="K72" t="n">
@@ -10531,13 +10543,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10564,7 +10576,7 @@
       <c r="I73" t="n">
         <v>9.65</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K73" t="n">
@@ -10601,52 +10613,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40059</v>
       </c>
       <c r="C2" t="n">
@@ -10675,10 +10687,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40126</v>
       </c>
       <c r="C3" t="n">
@@ -10707,10 +10719,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C4" t="n">
@@ -10739,10 +10751,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="C5" t="n">
@@ -10771,10 +10783,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40399</v>
       </c>
       <c r="C6" t="n">
@@ -10803,10 +10815,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40486</v>
       </c>
       <c r="C7" t="n">
@@ -10835,10 +10847,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40592</v>
       </c>
       <c r="C8" t="n">
@@ -10867,10 +10879,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40667</v>
       </c>
       <c r="C9" t="n">
@@ -10899,10 +10911,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="C10" t="n">
@@ -10931,10 +10943,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40844</v>
       </c>
       <c r="C11" t="n">
@@ -10963,10 +10975,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40952</v>
       </c>
       <c r="C12" t="n">
@@ -10995,10 +11007,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41023</v>
       </c>
       <c r="C13" t="n">
@@ -11027,10 +11039,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41114</v>
       </c>
       <c r="C14" t="n">
@@ -11059,10 +11071,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41204</v>
       </c>
       <c r="C15" t="n">
@@ -11091,10 +11103,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C16" t="n">
@@ -11123,10 +11135,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="C17" t="n">
@@ -11155,10 +11167,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41478</v>
       </c>
       <c r="C18" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41570</v>
       </c>
       <c r="C19" t="n">
@@ -11219,10 +11231,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="C20" t="n">
@@ -11251,10 +11263,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="C21" t="n">
@@ -11283,10 +11295,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="C22" t="n">
@@ -11315,10 +11327,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="C23" t="n">
@@ -11347,10 +11359,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="C24" t="n">
@@ -11379,10 +11391,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="C25" t="n">
@@ -11411,10 +11423,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C26" t="n">
@@ -11443,10 +11455,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42300</v>
       </c>
       <c r="C27" t="n">
@@ -11475,10 +11487,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C28" t="n">
@@ -11507,10 +11519,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42482</v>
       </c>
       <c r="C29" t="n">
@@ -11539,10 +11551,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42573</v>
       </c>
       <c r="C30" t="n">
@@ -11571,10 +11583,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42671</v>
       </c>
       <c r="C31" t="n">
@@ -11603,10 +11615,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="C32" t="n">
@@ -11635,10 +11647,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C33" t="n">
@@ -11667,10 +11679,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42944</v>
       </c>
       <c r="C34" t="n">
@@ -11699,10 +11711,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43035</v>
       </c>
       <c r="C35" t="n">
@@ -11731,10 +11743,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="C36" t="n">
@@ -11763,10 +11775,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43217</v>
       </c>
       <c r="C37" t="n">
@@ -11795,10 +11807,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43306</v>
       </c>
       <c r="C38" t="n">
@@ -11827,10 +11839,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43399</v>
       </c>
       <c r="C39" t="n">
@@ -11859,10 +11871,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C40" t="n">
@@ -11891,10 +11903,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43579</v>
       </c>
       <c r="C41" t="n">
@@ -11923,10 +11935,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43672</v>
       </c>
       <c r="C42" t="n">
@@ -11955,10 +11967,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43768</v>
       </c>
       <c r="C43" t="n">
@@ -11987,10 +11999,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43867</v>
       </c>
       <c r="C44" t="n">
@@ -12019,10 +12031,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43952</v>
       </c>
       <c r="C45" t="n">
@@ -12051,10 +12063,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C46" t="n">
@@ -12083,10 +12095,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44134</v>
       </c>
       <c r="C47" t="n">
@@ -12115,10 +12127,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44238</v>
       </c>
       <c r="C48" t="n">
@@ -12147,10 +12159,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44314</v>
       </c>
       <c r="C49" t="n">
@@ -12179,10 +12191,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44405</v>
       </c>
       <c r="C50" t="n">
@@ -12211,10 +12223,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C51" t="n">
@@ -12243,10 +12255,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44603</v>
       </c>
       <c r="C52" t="n">
@@ -12275,10 +12287,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44680</v>
       </c>
       <c r="C53" t="n">
@@ -12307,10 +12319,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C54" t="n">
@@ -12339,10 +12351,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="C55" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C56" t="n">
@@ -12403,10 +12415,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45048</v>
       </c>
       <c r="C57" t="n">
@@ -12435,10 +12447,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45142</v>
       </c>
       <c r="C58" t="n">
@@ -12467,10 +12479,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45233</v>
       </c>
       <c r="C59" t="n">
@@ -12499,10 +12511,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45336</v>
       </c>
       <c r="C60" t="n">
@@ -12531,10 +12543,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="C61" t="n">
@@ -12563,10 +12575,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="C62" t="n">
@@ -12595,10 +12607,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45595</v>
       </c>
       <c r="C63" t="n">
@@ -12627,10 +12639,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45700</v>
       </c>
       <c r="C64" t="n">
@@ -12659,10 +12671,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45779</v>
       </c>
       <c r="C65" t="n">
@@ -12691,10 +12703,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12723,10 +12735,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C67" t="n">
@@ -12755,10 +12767,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="C68" t="n">
@@ -12787,10 +12799,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46153</v>
       </c>
       <c r="C69" t="n">
@@ -12819,10 +12831,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C70" t="n">
@@ -12869,12 +12881,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/SYK.xlsx
+++ b/salidas/empresas/SYK.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>39.68035888671875</v>
+        <v>39.68034744262695</v>
       </c>
       <c r="C2" t="n">
         <v>49.90000152587891</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>36.75402069091797</v>
+        <v>36.75400161743164</v>
       </c>
       <c r="C3" t="n">
         <v>46.22000122070312</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>35.25902938842773</v>
+        <v>35.25904083251953</v>
       </c>
       <c r="C4" t="n">
         <v>44.34000015258789</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>34.78987121582031</v>
+        <v>34.78988647460938</v>
       </c>
       <c r="C5" t="n">
         <v>43.75</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>34.90917205810547</v>
+        <v>34.90914154052734</v>
       </c>
       <c r="C6" t="n">
         <v>43.90000152587891</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>33.48574447631836</v>
+        <v>33.48575592041016</v>
       </c>
       <c r="C7" t="n">
         <v>42.11000061035156</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>36.18943023681641</v>
+        <v>36.18940734863281</v>
       </c>
       <c r="C8" t="n">
         <v>45.5099983215332</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>39.43381881713867</v>
+        <v>39.43381500244141</v>
       </c>
       <c r="C10" t="n">
         <v>49.59000015258789</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>41.58083724975586</v>
+        <v>41.58086395263672</v>
       </c>
       <c r="C11" t="n">
         <v>52.29000091552734</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>41.23892211914062</v>
+        <v>41.23894119262695</v>
       </c>
       <c r="C12" t="n">
         <v>51.86000061035156</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>43.99886322021484</v>
+        <v>43.99885940551758</v>
       </c>
       <c r="C13" t="n">
         <v>55.11000061035156</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>49.45181274414062</v>
+        <v>49.45180892944336</v>
       </c>
       <c r="C14" t="n">
         <v>61.93999862670898</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>49.51569366455078</v>
+        <v>49.51568984985352</v>
       </c>
       <c r="C15" t="n">
         <v>62.02000045776367</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>52.94872283935547</v>
+        <v>52.9487190246582</v>
       </c>
       <c r="C16" t="n">
         <v>66.31999969482422</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>51.84696960449219</v>
+        <v>51.84695816040039</v>
       </c>
       <c r="C17" t="n">
         <v>64.94000244140625</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>53.73912811279297</v>
+        <v>53.73913955688477</v>
       </c>
       <c r="C18" t="n">
         <v>67.30999755859375</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>50.36994934082031</v>
+        <v>50.36996078491211</v>
       </c>
       <c r="C19" t="n">
         <v>63.09000015258789</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>49.84299850463867</v>
+        <v>49.843017578125</v>
       </c>
       <c r="C20" t="n">
         <v>62.43000030517578</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>53.33196258544922</v>
+        <v>53.33195114135742</v>
       </c>
       <c r="C21" t="n">
         <v>66.80000305175781</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>54.89677810668945</v>
+        <v>54.89677047729492</v>
       </c>
       <c r="C22" t="n">
         <v>68.76000213623047</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>56.68515777587891</v>
+        <v>56.68515396118164</v>
       </c>
       <c r="C23" t="n">
         <v>71</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>57.98649978637695</v>
+        <v>57.98650741577148</v>
       </c>
       <c r="C24" t="n">
         <v>72.62999725341797</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>59.91365051269531</v>
+        <v>59.91365814208984</v>
       </c>
       <c r="C25" t="n">
         <v>74.72000122070312</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>52.20795822143555</v>
+        <v>52.20794677734375</v>
       </c>
       <c r="C27" t="n">
         <v>65.11000061035156</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>52.15983200073242</v>
+        <v>52.15983581542969</v>
       </c>
       <c r="C28" t="n">
         <v>65.05000305175781</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>51.98342895507812</v>
+        <v>51.98343276977539</v>
       </c>
       <c r="C29" t="n">
         <v>64.83000183105469</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>51.7589225769043</v>
+        <v>51.75895309448242</v>
       </c>
       <c r="C30" t="n">
         <v>64.55000305175781</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>50.41984939575195</v>
+        <v>50.41983413696289</v>
       </c>
       <c r="C31" t="n">
         <v>62.88000106811523</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>51.47025299072266</v>
+        <v>51.47025680541992</v>
       </c>
       <c r="C32" t="n">
         <v>64.19000244140625</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>53.87580108642578</v>
+        <v>53.87578964233398</v>
       </c>
       <c r="C33" t="n">
         <v>67.19000244140625</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>49.95476531982422</v>
+        <v>49.95478439331055</v>
       </c>
       <c r="C34" t="n">
         <v>62.29999923706055</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>31.20770454406738</v>
+        <v>31.20770072937012</v>
       </c>
       <c r="C36" t="n">
         <v>38.91999816894531</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>32.35866165161133</v>
+        <v>32.35863876342773</v>
       </c>
       <c r="C37" t="n">
         <v>39.95000076293945</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>34.2135009765625</v>
+        <v>34.21349334716797</v>
       </c>
       <c r="C38" t="n">
         <v>42.2400016784668</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>27.27197456359863</v>
+        <v>27.27198219299316</v>
       </c>
       <c r="C39" t="n">
         <v>33.66999816894531</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>31.35426902770996</v>
+        <v>31.35428237915039</v>
       </c>
       <c r="C41" t="n">
         <v>38.70999908447266</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>31.13557815551758</v>
+        <v>31.13558578491211</v>
       </c>
       <c r="C42" t="n">
         <v>38.43999862670898</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>32.18854904174805</v>
+        <v>32.18855667114258</v>
       </c>
       <c r="C43" t="n">
         <v>39.7400016784668</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>33.58171463012695</v>
+        <v>33.58171844482422</v>
       </c>
       <c r="C45" t="n">
         <v>41.45999908447266</v>
@@ -1359,7 +1359,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>37.25902557373047</v>
+        <v>37.259033203125</v>
       </c>
       <c r="C47" t="n">
         <v>46</v>
@@ -1384,7 +1384,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>40.90614318847656</v>
+        <v>40.9061393737793</v>
       </c>
       <c r="C48" t="n">
         <v>50.40000152587891</v>
@@ -1409,7 +1409,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>41.00207901000977</v>
+        <v>41.0020751953125</v>
       </c>
       <c r="C49" t="n">
         <v>50.36999893188477</v>
@@ -1434,7 +1434,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>42.26379776000977</v>
+        <v>42.26379013061523</v>
       </c>
       <c r="C50" t="n">
         <v>51.91999816894531</v>
@@ -1459,7 +1459,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>43.22434616088867</v>
+        <v>43.22433853149414</v>
       </c>
       <c r="C51" t="n">
         <v>53.09999847412109</v>
@@ -1484,7 +1484,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>46.69954681396484</v>
+        <v>46.69953918457031</v>
       </c>
       <c r="C52" t="n">
         <v>57.22000122070312</v>
@@ -1509,7 +1509,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>46.87908935546875</v>
+        <v>46.87908554077148</v>
       </c>
       <c r="C53" t="n">
         <v>57.43999862670898</v>
@@ -1534,7 +1534,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>43.27991104125977</v>
+        <v>43.27992248535156</v>
       </c>
       <c r="C54" t="n">
         <v>53.02999877929688</v>
@@ -1559,7 +1559,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>40.97867584228516</v>
+        <v>40.97867202758789</v>
       </c>
       <c r="C55" t="n">
         <v>50.06000137329102</v>
@@ -1584,7 +1584,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>38.12178802490234</v>
+        <v>38.12179946899414</v>
       </c>
       <c r="C56" t="n">
         <v>46.56999969482422</v>
@@ -1609,7 +1609,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>35.35495376586914</v>
+        <v>35.35494995117188</v>
       </c>
       <c r="C57" t="n">
         <v>43.18999862670898</v>
@@ -1634,7 +1634,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>41.09590530395508</v>
+        <v>41.09589385986328</v>
       </c>
       <c r="C58" t="n">
         <v>50.04999923706055</v>
@@ -1659,7 +1659,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>40.63609313964844</v>
+        <v>40.63608169555664</v>
       </c>
       <c r="C59" t="n">
         <v>49.4900016784668</v>
@@ -1684,7 +1684,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>41.12875366210938</v>
+        <v>41.12874603271484</v>
       </c>
       <c r="C60" t="n">
         <v>50.09000015258789</v>
@@ -1734,7 +1734,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>47.42026901245117</v>
+        <v>47.42026138305664</v>
       </c>
       <c r="C62" t="n">
         <v>57.56000137329102</v>
@@ -1759,7 +1759,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>52.11614227294922</v>
+        <v>52.11614990234375</v>
       </c>
       <c r="C63" t="n">
         <v>63.2599983215332</v>
@@ -1817,7 +1817,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>48.75114440917969</v>
+        <v>48.75114059448242</v>
       </c>
       <c r="C65" t="n">
         <v>59</v>
@@ -1846,7 +1846,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>51.56052398681641</v>
+        <v>51.56052017211914</v>
       </c>
       <c r="C66" t="n">
         <v>62.40000152587891</v>
@@ -1875,7 +1875,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>48.6461181640625</v>
+        <v>48.64609909057617</v>
       </c>
       <c r="C67" t="n">
         <v>58.68999862670898</v>
@@ -1904,7 +1904,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>45.04054641723633</v>
+        <v>45.04053497314453</v>
       </c>
       <c r="C68" t="n">
         <v>54.34000015258789</v>
@@ -1933,7 +1933,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>40.48178863525391</v>
+        <v>40.48177719116211</v>
       </c>
       <c r="C69" t="n">
         <v>48.84000015258789</v>
@@ -1962,7 +1962,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>39.20799255371094</v>
+        <v>39.20798873901367</v>
       </c>
       <c r="C70" t="n">
         <v>47.13000106811523</v>
@@ -2020,7 +2020,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>40.62223434448242</v>
+        <v>40.62224960327148</v>
       </c>
       <c r="C72" t="n">
         <v>48.83000183105469</v>
@@ -2049,7 +2049,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>41.53120040893555</v>
+        <v>41.53119277954102</v>
       </c>
       <c r="C73" t="n">
         <v>49.70999908447266</v>
@@ -2078,7 +2078,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>46.31009674072266</v>
+        <v>46.31008529663086</v>
       </c>
       <c r="C74" t="n">
         <v>55.43000030517578</v>
@@ -2107,7 +2107,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>44.81459808349609</v>
+        <v>44.81461334228516</v>
       </c>
       <c r="C75" t="n">
         <v>53.63999938964844</v>
@@ -2136,7 +2136,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>46.53095245361328</v>
+        <v>46.53096389770508</v>
       </c>
       <c r="C76" t="n">
         <v>55.47999954223633</v>
@@ -2165,7 +2165,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>45.76773834228516</v>
+        <v>45.76775360107422</v>
       </c>
       <c r="C77" t="n">
         <v>54.56999969482422</v>
@@ -2194,7 +2194,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>43.15099716186523</v>
+        <v>43.15100479125977</v>
       </c>
       <c r="C78" t="n">
         <v>51.45000076293945</v>
@@ -2223,7 +2223,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>46.39587020874023</v>
+        <v>46.3958625793457</v>
       </c>
       <c r="C79" t="n">
         <v>55.09999847412109</v>
@@ -2252,7 +2252,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>43.81083679199219</v>
+        <v>43.81082916259766</v>
       </c>
       <c r="C80" t="n">
         <v>52.02999877929688</v>
@@ -2281,7 +2281,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>44.84653472900391</v>
+        <v>44.84652709960938</v>
       </c>
       <c r="C81" t="n">
         <v>53.2599983215332</v>
@@ -2310,7 +2310,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>47.04642105102539</v>
+        <v>47.04644012451172</v>
       </c>
       <c r="C82" t="n">
         <v>55.65999984741211</v>
@@ -2339,7 +2339,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>44.45997619628906</v>
+        <v>44.45996475219727</v>
       </c>
       <c r="C83" t="n">
         <v>52.59999847412109</v>
@@ -2368,7 +2368,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>45.77854919433594</v>
+        <v>45.77855682373047</v>
       </c>
       <c r="C84" t="n">
         <v>54.15999984741211</v>
@@ -2397,7 +2397,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>46.55900955200195</v>
+        <v>46.55900573730469</v>
       </c>
       <c r="C85" t="n">
         <v>54.81999969482422</v>
@@ -2455,7 +2455,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>54.25370788574219</v>
+        <v>54.25372695922852</v>
       </c>
       <c r="C87" t="n">
         <v>63.88000106811523</v>
@@ -2484,7 +2484,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>55.63722991943359</v>
+        <v>55.63722610473633</v>
       </c>
       <c r="C88" t="n">
         <v>65.23999786376953</v>
@@ -2513,7 +2513,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>55.92718505859375</v>
+        <v>55.92720031738281</v>
       </c>
       <c r="C89" t="n">
         <v>65.58000183105469</v>
@@ -2542,7 +2542,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>56.61796188354492</v>
+        <v>56.61797714233398</v>
       </c>
       <c r="C90" t="n">
         <v>66.38999938964844</v>
@@ -2571,7 +2571,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>55.38584518432617</v>
+        <v>55.38584136962891</v>
       </c>
       <c r="C91" t="n">
         <v>64.68000030517578</v>
@@ -2600,7 +2600,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>60.33531188964844</v>
+        <v>60.33528518676758</v>
       </c>
       <c r="C92" t="n">
         <v>70.45999908447266</v>
@@ -2629,7 +2629,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>57.27828598022461</v>
+        <v>57.27827453613281</v>
       </c>
       <c r="C93" t="n">
         <v>66.88999938964844</v>
@@ -2658,7 +2658,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>58.10151290893555</v>
+        <v>58.10152053833008</v>
       </c>
       <c r="C94" t="n">
         <v>67.58999633789062</v>
@@ -2687,7 +2687,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>63.49130249023438</v>
+        <v>63.49132537841797</v>
       </c>
       <c r="C95" t="n">
         <v>73.86000061035156</v>
@@ -2716,7 +2716,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>63.97271728515625</v>
+        <v>63.97268676757812</v>
       </c>
       <c r="C96" t="n">
         <v>74.41999816894531</v>
@@ -2745,7 +2745,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>64.85400390625</v>
+        <v>64.85398101806641</v>
       </c>
       <c r="C97" t="n">
         <v>75.13999938964844</v>
@@ -2774,7 +2774,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>66.97726440429688</v>
+        <v>66.97724914550781</v>
       </c>
       <c r="C98" t="n">
         <v>77.59999847412109</v>
@@ -2803,7 +2803,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>69.25586700439453</v>
+        <v>69.25584411621094</v>
       </c>
       <c r="C99" t="n">
         <v>80.23999786376953</v>
@@ -2832,7 +2832,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>70.58798217773438</v>
+        <v>70.58795166015625</v>
       </c>
       <c r="C100" t="n">
         <v>81.47000122070312</v>
@@ -2861,7 +2861,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>67.36484527587891</v>
+        <v>67.3648681640625</v>
       </c>
       <c r="C101" t="n">
         <v>77.75</v>
@@ -2890,7 +2890,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>73.20461273193359</v>
+        <v>73.20458221435547</v>
       </c>
       <c r="C102" t="n">
         <v>84.48999786376953</v>
@@ -2919,7 +2919,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>73.31885528564453</v>
+        <v>73.31887054443359</v>
       </c>
       <c r="C103" t="n">
         <v>84.31999969482422</v>
@@ -2977,7 +2977,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>72.44064331054688</v>
+        <v>72.44062042236328</v>
       </c>
       <c r="C105" t="n">
         <v>83.30999755859375</v>
@@ -3006,7 +3006,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>70.47928619384766</v>
+        <v>70.479248046875</v>
       </c>
       <c r="C106" t="n">
         <v>80.75</v>
@@ -3035,7 +3035,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>76.39690399169922</v>
+        <v>76.39691162109375</v>
       </c>
       <c r="C107" t="n">
         <v>87.52999877929688</v>
@@ -3064,7 +3064,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>81.09259796142578</v>
+        <v>81.09258270263672</v>
       </c>
       <c r="C108" t="n">
         <v>92.91000366210938</v>
@@ -3093,7 +3093,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>82.63008880615234</v>
+        <v>82.63008117675781</v>
       </c>
       <c r="C109" t="n">
         <v>94.33000183105469</v>
@@ -3122,7 +3122,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>79.75688934326172</v>
+        <v>79.75688171386719</v>
       </c>
       <c r="C110" t="n">
         <v>91.05000305175781</v>
@@ -3180,7 +3180,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>81.11381530761719</v>
+        <v>81.11380767822266</v>
       </c>
       <c r="C112" t="n">
         <v>92.25</v>
@@ -3209,7 +3209,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>81.10501098632812</v>
+        <v>81.10500335693359</v>
       </c>
       <c r="C113" t="n">
         <v>92.23999786376953</v>
@@ -3238,7 +3238,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>84.52542114257812</v>
+        <v>84.52541351318359</v>
       </c>
       <c r="C114" t="n">
         <v>96.12999725341797</v>
@@ -3267,7 +3267,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>84.33467102050781</v>
+        <v>84.33467864990234</v>
       </c>
       <c r="C115" t="n">
         <v>95.56999969482422</v>
@@ -3296,7 +3296,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>90.24700927734375</v>
+        <v>90.24701690673828</v>
       </c>
       <c r="C116" t="n">
         <v>102.2699966430664</v>
@@ -3325,7 +3325,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>87.05260467529297</v>
+        <v>87.05257415771484</v>
       </c>
       <c r="C117" t="n">
         <v>98.65000152587891</v>
@@ -3354,7 +3354,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>83.33420562744141</v>
+        <v>83.33415985107422</v>
       </c>
       <c r="C118" t="n">
         <v>94.09999847412109</v>
@@ -3383,7 +3383,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>84.6802978515625</v>
+        <v>84.68028259277344</v>
       </c>
       <c r="C119" t="n">
         <v>95.62000274658203</v>
@@ -3441,7 +3441,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>82.64116668701172</v>
+        <v>82.64115142822266</v>
       </c>
       <c r="C121" t="n">
         <v>92.94000244140625</v>
@@ -3470,7 +3470,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>88.16302490234375</v>
+        <v>88.16303253173828</v>
       </c>
       <c r="C122" t="n">
         <v>99.15000152587891</v>
@@ -3499,7 +3499,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>88.81211853027344</v>
+        <v>88.81212615966797</v>
       </c>
       <c r="C123" t="n">
         <v>99.87999725341797</v>
@@ -3528,7 +3528,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>95.74733734130859</v>
+        <v>95.74732208251953</v>
       </c>
       <c r="C124" t="n">
         <v>107.2900009155273</v>
@@ -3557,7 +3557,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>97.28227233886719</v>
+        <v>97.28230285644531</v>
       </c>
       <c r="C125" t="n">
         <v>109.0100021362305</v>
@@ -3586,7 +3586,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>99.20100402832031</v>
+        <v>99.20096588134766</v>
       </c>
       <c r="C126" t="n">
         <v>111.1600036621094</v>
@@ -3615,7 +3615,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>107.2934417724609</v>
+        <v>107.2934265136719</v>
       </c>
       <c r="C127" t="n">
         <v>119.8300018310547</v>
@@ -3644,7 +3644,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>104.1148529052734</v>
+        <v>104.1148376464844</v>
       </c>
       <c r="C128" t="n">
         <v>116.2799987792969</v>
@@ -3673,7 +3673,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>103.5597076416016</v>
+        <v>103.5596923828125</v>
       </c>
       <c r="C129" t="n">
         <v>115.6600036621094</v>
@@ -3702,7 +3702,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>104.5685653686523</v>
+        <v>104.5685501098633</v>
       </c>
       <c r="C130" t="n">
         <v>116.4100036621094</v>
@@ -3731,7 +3731,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>103.6164169311523</v>
+        <v>103.6163787841797</v>
       </c>
       <c r="C131" t="n">
         <v>115.3499984741211</v>
@@ -3876,7 +3876,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>119.0569534301758</v>
+        <v>119.0569763183594</v>
       </c>
       <c r="C136" t="n">
         <v>131.6499938964844</v>
@@ -3905,7 +3905,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>123.3254776000977</v>
+        <v>123.3255004882812</v>
       </c>
       <c r="C137" t="n">
         <v>136.3699951171875</v>
@@ -3963,7 +3963,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>125.8882446289062</v>
+        <v>125.8882751464844</v>
       </c>
       <c r="C139" t="n">
         <v>138.7799987792969</v>
@@ -4050,7 +4050,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>129.2168273925781</v>
+        <v>129.2168121337891</v>
       </c>
       <c r="C142" t="n">
         <v>142.0200042724609</v>
@@ -4079,7 +4079,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>140.9084014892578</v>
+        <v>140.9083557128906</v>
       </c>
       <c r="C143" t="n">
         <v>154.8699951171875</v>
@@ -4108,7 +4108,7 @@
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>141.9365692138672</v>
+        <v>141.9365234375</v>
       </c>
       <c r="C144" t="n">
         <v>156</v>
@@ -4137,7 +4137,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>141.3078460693359</v>
+        <v>141.3078765869141</v>
       </c>
       <c r="C145" t="n">
         <v>154.8399963378906</v>
@@ -4166,7 +4166,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>150.0141143798828</v>
+        <v>150.0142211914062</v>
       </c>
       <c r="C146" t="n">
         <v>164.3800048828125</v>
@@ -4195,7 +4195,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>147.9881134033203</v>
+        <v>147.9881896972656</v>
       </c>
       <c r="C147" t="n">
         <v>162.1600036621094</v>
@@ -4253,7 +4253,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>155.0733489990234</v>
+        <v>155.0733795166016</v>
       </c>
       <c r="C149" t="n">
         <v>169.4199981689453</v>
@@ -4282,7 +4282,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>159.2838134765625</v>
+        <v>159.2838592529297</v>
       </c>
       <c r="C150" t="n">
         <v>174.0200042724609</v>
@@ -4340,7 +4340,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>149.8421783447266</v>
+        <v>149.8422393798828</v>
       </c>
       <c r="C152" t="n">
         <v>163.25</v>
@@ -4369,7 +4369,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>155.5146331787109</v>
+        <v>155.5146026611328</v>
       </c>
       <c r="C153" t="n">
         <v>169.4299926757812</v>
@@ -4398,7 +4398,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>163.5242462158203</v>
+        <v>163.5242767333984</v>
       </c>
       <c r="C154" t="n">
         <v>177.6799926757812</v>
@@ -4427,7 +4427,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>149.2959594726562</v>
+        <v>149.2959747314453</v>
       </c>
       <c r="C155" t="n">
         <v>162.2200012207031</v>
@@ -4456,7 +4456,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>161.4811401367188</v>
+        <v>161.4811248779297</v>
       </c>
       <c r="C156" t="n">
         <v>175.4600067138672</v>
@@ -4485,7 +4485,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>144.7486114501953</v>
+        <v>144.7486572265625</v>
       </c>
       <c r="C157" t="n">
         <v>156.75</v>
@@ -4514,7 +4514,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>163.9745483398438</v>
+        <v>163.9745635986328</v>
       </c>
       <c r="C158" t="n">
         <v>177.5700073242188</v>
@@ -4543,7 +4543,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>174.0769653320312</v>
+        <v>174.0769500732422</v>
       </c>
       <c r="C159" t="n">
         <v>188.5099945068359</v>
@@ -4572,7 +4572,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>182.8818664550781</v>
+        <v>182.8817901611328</v>
       </c>
       <c r="C160" t="n">
         <v>197.5200042724609</v>
@@ -4601,7 +4601,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>174.909912109375</v>
+        <v>174.9098968505859</v>
       </c>
       <c r="C161" t="n">
         <v>188.9100036621094</v>
@@ -4630,7 +4630,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>169.6601257324219</v>
+        <v>169.66015625</v>
       </c>
       <c r="C162" t="n">
         <v>183.2400054931641</v>
@@ -4659,7 +4659,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>190.8348541259766</v>
+        <v>190.8348693847656</v>
       </c>
       <c r="C163" t="n">
         <v>205.5800018310547</v>
@@ -4717,7 +4717,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>204.8332672119141</v>
+        <v>204.8332824707031</v>
       </c>
       <c r="C165" t="n">
         <v>220.6600036621094</v>
@@ -4746,7 +4746,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>201.2696228027344</v>
+        <v>201.2696533203125</v>
       </c>
       <c r="C166" t="n">
         <v>216.3000030517578</v>
@@ -4775,7 +4775,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>201.2417602539062</v>
+        <v>201.24169921875</v>
       </c>
       <c r="C167" t="n">
         <v>216.2700042724609</v>
@@ -4804,7 +4804,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>190.6245880126953</v>
+        <v>190.6245574951172</v>
       </c>
       <c r="C168" t="n">
         <v>204.8600006103516</v>
@@ -4833,7 +4833,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>195.8865203857422</v>
+        <v>195.8865509033203</v>
       </c>
       <c r="C169" t="n">
         <v>209.9400024414062</v>
@@ -4891,7 +4891,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>177.8318328857422</v>
+        <v>177.8318481445312</v>
       </c>
       <c r="C171" t="n">
         <v>190.5899963378906</v>
@@ -5007,7 +5007,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>169.2976226806641</v>
+        <v>169.297607421875</v>
       </c>
       <c r="C175" t="n">
         <v>180.1900024414062</v>
@@ -5036,7 +5036,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>181.6151580810547</v>
+        <v>181.6151123046875</v>
       </c>
       <c r="C176" t="n">
         <v>193.3000030517578</v>
@@ -5065,7 +5065,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>186.1813507080078</v>
+        <v>186.1813201904297</v>
       </c>
       <c r="C177" t="n">
         <v>198.1600036621094</v>
@@ -5123,7 +5123,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>190.3266906738281</v>
+        <v>190.3266754150391</v>
       </c>
       <c r="C179" t="n">
         <v>202.0099945068359</v>
@@ -5152,7 +5152,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>219.9012145996094</v>
+        <v>219.9011993408203</v>
       </c>
       <c r="C180" t="n">
         <v>233.3999938964844</v>
@@ -5181,7 +5181,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>231.4735107421875</v>
+        <v>231.4734802246094</v>
       </c>
       <c r="C181" t="n">
         <v>245.0399932861328</v>
@@ -5210,7 +5210,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>208.7738800048828</v>
+        <v>208.7739105224609</v>
       </c>
       <c r="C182" t="n">
         <v>221.0099945068359</v>
@@ -5239,7 +5239,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>229.2536163330078</v>
+        <v>229.2535858154297</v>
       </c>
       <c r="C183" t="n">
         <v>242.6900024414062</v>
@@ -5297,7 +5297,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>248.7370910644531</v>
+        <v>248.7371063232422</v>
       </c>
       <c r="C185" t="n">
         <v>262.6300048828125</v>
@@ -5326,7 +5326,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>241.7664031982422</v>
+        <v>241.7664184570312</v>
       </c>
       <c r="C186" t="n">
         <v>255.2700042724609</v>
@@ -5355,7 +5355,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>246.5871887207031</v>
+        <v>246.587158203125</v>
       </c>
       <c r="C187" t="n">
         <v>259.7300109863281</v>
@@ -5413,7 +5413,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>263.0782470703125</v>
+        <v>263.0782165527344</v>
       </c>
       <c r="C189" t="n">
         <v>277.1000061035156</v>
@@ -5442,7 +5442,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>250.9656066894531</v>
+        <v>250.9655914306641</v>
       </c>
       <c r="C190" t="n">
         <v>263.7200012207031</v>
@@ -5471,7 +5471,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>253.2019653320312</v>
+        <v>253.2019805908203</v>
       </c>
       <c r="C191" t="n">
         <v>266.0700073242188</v>
@@ -5500,7 +5500,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>225.1857604980469</v>
+        <v>225.1857757568359</v>
       </c>
       <c r="C192" t="n">
         <v>236.6300048828125</v>
@@ -5529,7 +5529,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>255.1406402587891</v>
+        <v>255.1407470703125</v>
       </c>
       <c r="C193" t="n">
         <v>267.4200134277344</v>
@@ -5558,7 +5558,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>236.6601409912109</v>
+        <v>236.66015625</v>
       </c>
       <c r="C194" t="n">
         <v>248.0500030517578</v>
@@ -5616,7 +5616,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>255.7249450683594</v>
+        <v>255.7250366210938</v>
       </c>
       <c r="C196" t="n">
         <v>267.3500061035156</v>
@@ -5674,7 +5674,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>224.3033905029297</v>
+        <v>224.3034210205078</v>
       </c>
       <c r="C198" t="n">
         <v>234.5</v>
@@ -5703,7 +5703,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>190.9510040283203</v>
+        <v>190.9509887695312</v>
       </c>
       <c r="C199" t="n">
         <v>198.9299926757812</v>
@@ -5761,7 +5761,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>196.9694671630859</v>
+        <v>196.9694976806641</v>
       </c>
       <c r="C201" t="n">
         <v>205.1999969482422</v>
@@ -5790,7 +5790,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>195.0749206542969</v>
+        <v>195.0749053955078</v>
       </c>
       <c r="C202" t="n">
         <v>202.5399932861328</v>
@@ -5819,7 +5819,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>220.7908325195312</v>
+        <v>220.7908477783203</v>
       </c>
       <c r="C203" t="n">
         <v>229.2400054931641</v>
@@ -5848,7 +5848,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>225.2694549560547</v>
+        <v>225.2694396972656</v>
       </c>
       <c r="C204" t="n">
         <v>233.8899993896484</v>
@@ -5906,7 +5906,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>245.2162475585938</v>
+        <v>245.21630859375</v>
       </c>
       <c r="C206" t="n">
         <v>253.8099975585938</v>
@@ -5964,7 +5964,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>276.5476379394531</v>
+        <v>276.547607421875</v>
       </c>
       <c r="C208" t="n">
         <v>285.4700012207031</v>
@@ -6022,7 +6022,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>266.9667053222656</v>
+        <v>266.9667358398438</v>
       </c>
       <c r="C210" t="n">
         <v>275.5799865722656</v>
@@ -6051,7 +6051,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>296.2944641113281</v>
+        <v>296.2944030761719</v>
       </c>
       <c r="C211" t="n">
         <v>305.0899963378906</v>
@@ -6080,7 +6080,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>275.2394714355469</v>
+        <v>275.2395324707031</v>
       </c>
       <c r="C212" t="n">
         <v>283.4100036621094</v>
@@ -6109,7 +6109,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>275.37548828125</v>
+        <v>275.3754577636719</v>
       </c>
       <c r="C213" t="n">
         <v>283.5499877929688</v>
@@ -6138,7 +6138,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>266.1406555175781</v>
+        <v>266.1407165527344</v>
       </c>
       <c r="C214" t="n">
         <v>273.2699890136719</v>
@@ -6167,7 +6167,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>263.1702270507812</v>
+        <v>263.1702880859375</v>
       </c>
       <c r="C215" t="n">
         <v>270.2200012207031</v>
@@ -6225,7 +6225,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>292.4298400878906</v>
+        <v>292.4297790527344</v>
       </c>
       <c r="C217" t="n">
         <v>299.4599914550781</v>
@@ -6254,7 +6254,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>327.604248046875</v>
+        <v>327.6042175292969</v>
       </c>
       <c r="C218" t="n">
         <v>335.4800109863281</v>
@@ -6283,7 +6283,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>340.8751525878906</v>
+        <v>340.8751220703125</v>
       </c>
       <c r="C219" t="n">
         <v>349.0700073242188</v>
@@ -6457,7 +6457,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>353.5947875976562</v>
+        <v>353.5948181152344</v>
       </c>
       <c r="C225" t="n">
         <v>360.4200134277344</v>
@@ -6486,7 +6486,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>355.2076416015625</v>
+        <v>355.2076721191406</v>
       </c>
       <c r="C226" t="n">
         <v>361.260009765625</v>
@@ -6544,7 +6544,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>385.580078125</v>
+        <v>385.5801086425781</v>
       </c>
       <c r="C228" t="n">
         <v>392.1499938964844</v>
@@ -6660,7 +6660,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>367.711669921875</v>
+        <v>367.7116394042969</v>
       </c>
       <c r="C232" t="n">
         <v>372.25</v>
@@ -6689,7 +6689,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>369.3612670898438</v>
+        <v>369.3612976074219</v>
       </c>
       <c r="C233" t="n">
         <v>373.9200134277344</v>
@@ -6718,7 +6718,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>377.9749755859375</v>
+        <v>377.9749450683594</v>
       </c>
       <c r="C234" t="n">
         <v>382.6400146484375</v>
@@ -6892,7 +6892,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>368.2752990722656</v>
+        <v>368.2753295898438</v>
       </c>
       <c r="C240" t="n">
         <v>371.1799926757812</v>
@@ -6979,7 +6979,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>385.3856201171875</v>
+        <v>385.3855895996094</v>
       </c>
       <c r="C243" t="n">
         <v>387.4599914550781</v>
